--- a/Compititor's_Price/IKO_Prices/IKO_Prices_16-10-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_16-10-2025.xlsx
@@ -498,17 +498,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.50</t>
+          <t>£10.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.50</t>
+          <t>£10.45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.50</t>
+          <t>£10.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,17 +555,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.87</t>
+          <t>£11.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.87</t>
+          <t>£11.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.87</t>
+          <t>£11.83</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.33</t>
+          <t>£15.28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.33</t>
+          <t>£15.28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.33</t>
+          <t>£15.28</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.67</t>
+          <t>£15.59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.67</t>
+          <t>£15.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.67</t>
+          <t>£15.59</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£19.94</t>
+          <t>£19.85</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.94</t>
+          <t>£19.85</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£19.94</t>
+          <t>£19.85</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£21.95</t>
+          <t>£21.74</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£21.95</t>
+          <t>£21.74</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£21.95</t>
+          <t>£21.74</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.19</t>
+          <t>£25.10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.19</t>
+          <t>£25.10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.19</t>
+          <t>£25.10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£27.29</t>
+          <t>£27.20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.29</t>
+          <t>£27.20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£27.29</t>
+          <t>£27.20</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£27.20</t>
+          <t>£26.83</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£27.20</t>
+          <t>£26.83</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£36.86</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£36.86</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>£40.74</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>£42.41</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>£42.41</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£42.41</t>
+          <t>£40.74</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>£40.16</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>£40.22</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>£40.22</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£40.22</t>
+          <t>£40.16</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
